--- a/e_commerce_forms/009_led_mask_preorder_form--e_commerce_forms.xlsx
+++ b/e_commerce_forms/009_led_mask_preorder_form--e_commerce_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>special_instructions</t>
+          <t>special_instructions_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Special Instructions</t>
+          <t>Special Instructions 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>review_details</t>
+          <t>review_details_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Review Details</t>
+          <t>Review Details 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>review_agreement</t>
+          <t>review_agreement_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Review Agreement</t>
+          <t>Review Agreement 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>review_agreement_details</t>
+          <t>review_agreement_details_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Review Agreement Details</t>
+          <t>Review Agreement Details 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>customer_agreement</t>
+          <t>customer_agreement_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Customer Agreement</t>
+          <t>Customer Agreement 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>customer_agreement_details</t>
+          <t>customer_agreement_details_2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Customer Agreement Details</t>
+          <t>Customer Agreement Details 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>terms_and_conditions</t>
+          <t>terms_and_conditions_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Terms and Conditions</t>
+          <t>Terms And Conditions 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1193,7 +1193,7 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1320,7 +1320,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>review_agreement_choices</t>
+          <t>review_agreement_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1337,7 +1337,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>review_agreement_choices</t>
+          <t>review_agreement_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1354,7 +1354,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>customer_agreement_choices</t>
+          <t>customer_agreement_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>customer_agreement_choices</t>
+          <t>customer_agreement_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
